--- a/artfynd/A 38129-2021 artfynd.xlsx
+++ b/artfynd/A 38129-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 38129-2021 artfynd.xlsx
+++ b/artfynd/A 38129-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,16 +678,11 @@
         <v>90073066</v>
       </c>
       <c r="B2" t="n">
-        <v>56411</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -723,10 +718,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>531320.9137205731</v>
+        <v>531321</v>
       </c>
       <c r="R2" t="n">
-        <v>6486850.244933486</v>
+        <v>6486850</v>
       </c>
       <c r="S2" t="n">
         <v>5</v>
@@ -792,6 +787,343 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>106087793</v>
+      </c>
+      <c r="B3" t="n">
+        <v>57947</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>102977</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Gröngöling</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Picus viridis</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="M3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>Björklund, Ög</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>531321</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6486850</v>
+      </c>
+      <c r="S3" t="n">
+        <v>5</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2023-01-21</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Gunilla Wetterling</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Gunilla Wetterling</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>84143547</v>
+      </c>
+      <c r="B4" t="n">
+        <v>58497</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>102990</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Järnsparv</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Prunella modularis</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr"/>
+      <c r="L4" t="inlineStr"/>
+      <c r="M4" t="inlineStr"/>
+      <c r="N4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Björklund, Ög</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>531321</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6486850</v>
+      </c>
+      <c r="S4" t="n">
+        <v>5</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2020-04-05</t>
+        </is>
+      </c>
+      <c r="Z4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2020-04-05</t>
+        </is>
+      </c>
+      <c r="AB4" t="inlineStr">
+        <is>
+          <t>09:00</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Gunilla Wetterling</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Gunilla Wetterling, Svante Söderström</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>119606291</v>
+      </c>
+      <c r="B5" t="n">
+        <v>101326</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>222498</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Blåsippa</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Hepatica nobilis</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>Schreb.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Olstorps motionsområde Ö, Ög</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>531376</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6486900</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Linköping</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Östergötland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vreta kloster</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-08-31</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>blad</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI5" t="inlineStr">
+        <is>
+          <t>Område med gran och ek</t>
+        </is>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Monica Andersson</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
